--- a/Copper/6. Statistical data analysis/Multiple linear regression/Simple_MLR.xlsx
+++ b/Copper/6. Statistical data analysis/Multiple linear regression/Simple_MLR.xlsx
@@ -1,77 +1,87 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Copper/6. Statistical data analysis/Multiple linear regression/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_C4797D5B4E8567198E1FAA9AFC3550D3A5D5B075" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2689176C-48D9-46F1-80C8-63ED36148F85}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Coefficients" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Model_Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Coefficients" sheetId="1" r:id="rId1"/>
+    <sheet name="Model_Summary" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
-    <t xml:space="preserve">Term</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Std. Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pr(&gt;|t|)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Intercept)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Cu_nM_std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_DOC_nM_std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pH_std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residual standard error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R-squared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted R-squared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-statistic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numerator df</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denominator df</t>
+    <t>Term</t>
+  </si>
+  <si>
+    <t>Estimate</t>
+  </si>
+  <si>
+    <t>Std. Error</t>
+  </si>
+  <si>
+    <t>t value</t>
+  </si>
+  <si>
+    <t>Pr(&gt;|t|)</t>
+  </si>
+  <si>
+    <t>(Intercept)</t>
+  </si>
+  <si>
+    <t>log_Cu_nM_std</t>
+  </si>
+  <si>
+    <t>log_DOC_nM_std</t>
+  </si>
+  <si>
+    <t>pH_std</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Residual standard error</t>
+  </si>
+  <si>
+    <t>R-squared</t>
+  </si>
+  <si>
+    <t>Adjusted R-squared</t>
+  </si>
+  <si>
+    <t>F-statistic</t>
+  </si>
+  <si>
+    <t>Numerator df</t>
+  </si>
+  <si>
+    <t>Denominator df</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -100,14 +110,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -388,11 +414,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -409,86 +435,86 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="n">
-        <v>0.000000000000000421443523066134</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.00743142845575979</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.0000000000000567109709223522</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.999999999999955</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="B2" s="1">
+        <v>4.2144352306613402E-16</v>
+      </c>
+      <c r="C2" s="1">
+        <v>7.4314284557597896E-3</v>
+      </c>
+      <c r="D2" s="1">
+        <v>5.6710970922352201E-14</v>
+      </c>
+      <c r="E2">
+        <v>0.99999999999995504</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3">
         <v>1.30159224614806</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.0100794507633238</v>
-      </c>
-      <c r="D3" t="n">
-        <v>129.133251077943</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.38767320400735e-298</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="C3" s="1">
+        <v>1.00794507633238E-2</v>
+      </c>
+      <c r="D3" s="1">
+        <v>129.13325107794299</v>
+      </c>
+      <c r="E3">
+        <v>1.3876732040073501E-298</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="n">
-        <v>-0.63754172074934</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.00963265868122383</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-66.1854366325726</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000104811803600312</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4" s="2">
+        <v>-0.63754172074934001</v>
+      </c>
+      <c r="C4" s="1">
+        <v>9.6326586812238296E-3</v>
+      </c>
+      <c r="D4" s="1">
+        <v>-66.185436632572603</v>
+      </c>
+      <c r="E4">
+        <v>1.04811803600312E-200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="n">
-        <v>-0.53495690600957</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.00790597606319575</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="B5" s="2">
+        <v>-0.53495690600957002</v>
+      </c>
+      <c r="C5" s="1">
+        <v>7.9059760631957493E-3</v>
+      </c>
+      <c r="D5" s="1">
         <v>-67.6648780281444</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000770008103207652</v>
+      <c r="E5">
+        <v>7.7000810320765206E-204</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -496,56 +522,56 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>0.140215911671733</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.980505643200425</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="B3">
+        <v>0.98050564320042499</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="n">
-        <v>0.980339498114065</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4">
+        <v>0.98033949811406496</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="n">
-        <v>5901.50250411734</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5">
+        <v>5901.5025041173403</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>352</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Copper/6. Statistical data analysis/Multiple linear regression/Simple_MLR.xlsx
+++ b/Copper/6. Statistical data analysis/Multiple linear regression/Simple_MLR.xlsx
@@ -1,87 +1,77 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Copper/6. Statistical data analysis/Multiple linear regression/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_C4797D5B4E8567198E1FAA9AFC3550D3A5D5B075" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2689176C-48D9-46F1-80C8-63ED36148F85}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Coefficients" sheetId="1" r:id="rId1"/>
-    <sheet name="Model_Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="Coefficients" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Model_Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
-    <t>Term</t>
-  </si>
-  <si>
-    <t>Estimate</t>
-  </si>
-  <si>
-    <t>Std. Error</t>
-  </si>
-  <si>
-    <t>t value</t>
-  </si>
-  <si>
-    <t>Pr(&gt;|t|)</t>
-  </si>
-  <si>
-    <t>(Intercept)</t>
-  </si>
-  <si>
-    <t>log_Cu_nM_std</t>
-  </si>
-  <si>
-    <t>log_DOC_nM_std</t>
-  </si>
-  <si>
-    <t>pH_std</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Residual standard error</t>
-  </si>
-  <si>
-    <t>R-squared</t>
-  </si>
-  <si>
-    <t>Adjusted R-squared</t>
-  </si>
-  <si>
-    <t>F-statistic</t>
-  </si>
-  <si>
-    <t>Numerator df</t>
-  </si>
-  <si>
-    <t>Denominator df</t>
+    <t xml:space="preserve">Term</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Std. Error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pr(&gt;|t|)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Cu_nM_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_DOC_nM_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pH_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residual standard error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-squared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted R-squared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-statistic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numerator df</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denominator df</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -110,30 +100,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -414,11 +388,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,86 +409,86 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1">
-        <v>4.2144352306613402E-16</v>
-      </c>
-      <c r="C2" s="1">
-        <v>7.4314284557597896E-3</v>
-      </c>
-      <c r="D2" s="1">
-        <v>5.6710970922352201E-14</v>
-      </c>
-      <c r="E2">
-        <v>0.99999999999995504</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B2" t="n">
+        <v>-0.000000000000000446442147678248</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.00711829420868138</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.0000000000000627175745466902</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.99999999999995</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3">
-        <v>1.30159224614806</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1.00794507633238E-2</v>
-      </c>
-      <c r="D3" s="1">
-        <v>129.13325107794299</v>
-      </c>
-      <c r="E3">
-        <v>1.3876732040073501E-298</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B3" t="n">
+        <v>1.31361970828827</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.00979297068491283</v>
+      </c>
+      <c r="D3" t="n">
+        <v>134.139042232818</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.97626258336499e-323</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2">
-        <v>-0.63754172074934001</v>
-      </c>
-      <c r="C4" s="1">
-        <v>9.6326586812238296E-3</v>
-      </c>
-      <c r="D4" s="1">
-        <v>-66.185436632572603</v>
-      </c>
-      <c r="E4">
-        <v>1.04811803600312E-200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B4" t="n">
+        <v>-0.661123503297377</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.00938735339780437</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-70.4270389407102</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6.4536976714532e-221</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2">
-        <v>-0.53495690600957002</v>
-      </c>
-      <c r="C5" s="1">
-        <v>7.9059760631957493E-3</v>
-      </c>
-      <c r="D5" s="1">
-        <v>-67.6648780281444</v>
-      </c>
-      <c r="E5">
-        <v>7.7000810320765206E-204</v>
+      <c r="B5" t="n">
+        <v>-0.557304923981278</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.00758794078071161</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-73.4461351356267</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.10816157344942e-227</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -522,56 +496,56 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2">
-        <v>0.140215911671733</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B2" t="n">
+        <v>0.139852291373291</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3">
-        <v>0.98050564320042499</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B3" t="n">
+        <v>0.980593741767009</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="B4">
-        <v>0.98033949811406496</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" t="n">
+        <v>0.98044133659764</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="B5">
-        <v>5901.5025041173403</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B5" t="n">
+        <v>6434.12389374124</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7">
-        <v>352</v>
+      <c r="B7" t="n">
+        <v>382</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>